--- a/01-02_Quote_and_Energy_Model/Solar_Deal_Desk_Model.xlsx
+++ b/01-02_Quote_and_Energy_Model/Solar_Deal_Desk_Model.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Deal_Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">One-page output panel used for the proposal pack and interview demo.</t>
+    <t xml:space="preserve">One-page output panel used for the proposal pack and management presentation.</t>
   </si>
   <si>
     <t xml:space="preserve">COLOUR LEGEND</t>
